--- a/meldetabelle_mixitcup2026.xlsx
+++ b/meldetabelle_mixitcup2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nils\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Sport\HSP\Mix it-Cup '26\Webseite\mixitcup.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A3BCC4-3A5C-4144-ABA4-0E1FAB8581E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C794308-7416-4300-9831-9643DC4B79C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meldetabelle" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Stadt:</t>
   </si>
@@ -108,13 +108,22 @@
     </r>
   </si>
   <si>
+    <t>Bergische Universität Wuppertal</t>
+  </si>
+  <si>
+    <t>Ja (C-Lizenz)</t>
+  </si>
+  <si>
     <t>Ja</t>
   </si>
   <si>
-    <t>Bunte Universität Mixhausen</t>
-  </si>
-  <si>
-    <t>[4] Legendäre Limette</t>
+    <t>Damen L</t>
+  </si>
+  <si>
+    <t>Nein</t>
+  </si>
+  <si>
+    <t>[3] Beiendruckende Banane</t>
   </si>
 </sst>
 </file>
@@ -194,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,14 +226,53 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC59EE2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -235,7 +283,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -256,6 +304,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFC59EE2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -270,21 +346,125 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF81"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -306,21 +486,20 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF81"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -328,21 +507,13 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF81"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -350,67 +521,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF81"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF81"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFDE08D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="5" tint="0.79995117038483843"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -418,8 +543,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFF81"/>
-      <color rgb="FFFDE08D"/>
+      <color rgb="FFC59EE2"/>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFFFFF99"/>
     </mruColors>
   </colors>
   <extLst>
@@ -638,8 +764,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -768,21 +894,27 @@
       <c r="A8" s="3">
         <v>1</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>17</v>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
@@ -1333,61 +1465,56 @@
       <c r="J47" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Erdbeere">
-      <formula>NOT(ISERROR(SEARCH("Erdbeere",D8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="8" operator="containsText" text="Mandarine">
-      <formula>NOT(ISERROR(SEARCH("Mandarine",D8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Banane">
-      <formula>NOT(ISERROR(SEARCH("Banane",D8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="Limette">
-      <formula>NOT(ISERROR(SEARCH("Limette",D8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G47">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Damen">
-      <formula>NOT(ISERROR(SEARCH("Damen",G8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H47">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Damen">
-      <formula>NOT(ISERROR(SEARCH("Damen",H8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:H47">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Herren">
-      <formula>NOT(ISERROR(SEARCH("Herren",G8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E8:H47">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Nein">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="Nein">
       <formula>NOT(ISERROR(SEARCH("Nein",E8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F47">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH("Ja",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <conditionalFormatting sqref="D8:D47">
+    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="Mandarine">
+      <formula>NOT(ISERROR(SEARCH("Mandarine",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="Erdbeere">
+      <formula>NOT(ISERROR(SEARCH("Erdbeere",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Banane">
+      <formula>NOT(ISERROR(SEARCH("Banane",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Limette">
+      <formula>NOT(ISERROR(SEARCH("Limette",D8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E47">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH("Ja",E8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H47">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="Damen">
+      <formula>NOT(ISERROR(SEARCH("Damen",G8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Herren">
+      <formula>NOT(ISERROR(SEARCH("Herren",G8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Nein,Ja (keine Lizenz),Ja (GAU-Lizenz),Ja (C-Lizenz),Ja (B-Lizenz),Ja (A-Lizenz),Ja (I-Lizenz)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F47" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Ja,Nein"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H47" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:H47" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Nein,Damen XS,Damen S,Damen M,Damen L,Damen XL,Damen 2XL,Herren S,Herren M,Herren L,Herren XL,Herren 2XL,Herren 3XL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D8:D47" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"[1] Eifrige Erdbeere,[2] Mutige Mandarine,[3] Beiendruckende Banane,[4] Legendäre Limette,Unterstützer:in"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G47" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Nein,Damen XS,Damen S,Damen M,Damen L,Damen XL,Damen 2XL,Herren S,Herren M,Herren L,Herren XL,Herren 2XL,Herren 3XL,Herren 4XL,Herren 5XL"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/meldetabelle_mixitcup2026.xlsx
+++ b/meldetabelle_mixitcup2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Sport\HSP\Mix it-Cup '26\Webseite\mixitcup.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chill\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C794308-7416-4300-9831-9643DC4B79C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3FED56-447F-4AF3-A0A8-697E610F7339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,20 +117,20 @@
     <t>Ja</t>
   </si>
   <si>
-    <t>Damen L</t>
-  </si>
-  <si>
-    <t>Nein</t>
-  </si>
-  <si>
-    <t>[3] Beiendruckende Banane</t>
+    <t>Tailliert L</t>
+  </si>
+  <si>
+    <t>Unisex M</t>
+  </si>
+  <si>
+    <t>[4] Legendäre Limette</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -175,6 +175,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -223,14 +230,28 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="37">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2E2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -241,7 +262,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC59EE2"/>
+          <bgColor rgb="FFFFBDBD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC9A6E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -255,7 +283,168 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FFFEF994"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAC2EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFBDBD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF994"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF994"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF994"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF293"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF293"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -269,56 +458,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC59EE2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FFFFFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -332,49 +479,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -388,154 +493,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -543,9 +501,15 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFC59EE2"/>
-      <color rgb="FFFF99FF"/>
-      <color rgb="FFFFFF99"/>
+      <color rgb="FFE2E2E2"/>
+      <color rgb="FFDAC2EC"/>
+      <color rgb="FFFFBDBD"/>
+      <color rgb="FFC9A6E4"/>
+      <color rgb="FFFEF994"/>
+      <color rgb="FFFFF293"/>
+      <color rgb="FFFEDE00"/>
+      <color rgb="FF6084BF"/>
+      <color rgb="FFFFFF66"/>
     </mruColors>
   </colors>
   <extLst>
@@ -764,13 +728,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1465,41 +1429,41 @@
       <c r="J47" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E8:H47">
-    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="Nein">
-      <formula>NOT(ISERROR(SEARCH("Nein",E8)))</formula>
+  <conditionalFormatting sqref="D8:D47">
+    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="Erdbeere">
+      <formula>NOT(ISERROR(SEARCH("Erdbeere",D8)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F47">
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Ja">
-      <formula>NOT(ISERROR(SEARCH("Ja",F8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D47">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="Mandarine">
+    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Mandarine">
       <formula>NOT(ISERROR(SEARCH("Mandarine",D8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="Erdbeere">
-      <formula>NOT(ISERROR(SEARCH("Erdbeere",D8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Banane">
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="Banane">
       <formula>NOT(ISERROR(SEARCH("Banane",D8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Limette">
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="Limette">
       <formula>NOT(ISERROR(SEARCH("Limette",D8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E47">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Ja">
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Ja">
       <formula>NOT(ISERROR(SEARCH("Ja",E8)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F47">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="Ja">
+      <formula>NOT(ISERROR(SEARCH("Ja",F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G8:H47">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="Damen">
-      <formula>NOT(ISERROR(SEARCH("Damen",G8)))</formula>
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Tailliert">
+      <formula>NOT(ISERROR(SEARCH("Tailliert",G8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Herren">
-      <formula>NOT(ISERROR(SEARCH("Herren",G8)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Unisex">
+      <formula>NOT(ISERROR(SEARCH("Unisex",G8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:H47">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Nein">
+      <formula>NOT(ISERROR(SEARCH("Nein",E8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -1509,11 +1473,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F47" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Ja,Nein"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:H47" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Nein,Damen XS,Damen S,Damen M,Damen L,Damen XL,Damen 2XL,Herren S,Herren M,Herren L,Herren XL,Herren 2XL,Herren 3XL"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D8:D47" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"[1] Eifrige Erdbeere,[2] Mutige Mandarine,[3] Beiendruckende Banane,[4] Legendäre Limette,Unterstützer:in"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D8:D47" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"[1] Eifrige Erdbeere,[2] Mutige Mandarine,[3] Beiendruckende Banane,[4] Legendäre Limette,Unterstützer:in"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:H47" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>"Nein,Tailliert XS,Tailliert S,Tailliert M,Tailliert L,Tailliert XL,Tailliert 2XL,Unisex S,Unisex M,Unisex L,Unisex XL,Unisex 2XL,Unisex 3XL"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
